--- a/AI_Engineering_Curriculum_With_Resources.xlsx
+++ b/AI_Engineering_Curriculum_With_Resources.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{F727C118-7E57-8C44-AE34-C37553988A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EF0462B-7F91-CD42-8D95-4DEA92EF01FF}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dunnhumby-my.sharepoint.com/personal/dh219329_dunnhumby_com/Documents/Desktop/Learn AI/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{F727C118-7E57-8C44-AE34-C37553988A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13014DFF-2973-46DF-8BD1-EA932D291ED0}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -45,27 +50,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="603">
   <si>
     <t>AI Engineering Learning Path - Comprehensive Resource Guide</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>https://www.backprop.site/learning-ai</t>
-  </si>
-  <si>
-    <t>Last Updated:</t>
-  </si>
-  <si>
-    <t>February 9, 2026</t>
-  </si>
-  <si>
-    <t>Resources Curated:</t>
-  </si>
-  <si>
-    <t>February 10, 2026</t>
   </si>
   <si>
     <t>Total Topics:</t>
@@ -2038,18 +2025,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2066,6 +2053,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2353,26 +2344,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.97265625" customWidth="1"/>
-    <col min="2" max="2" width="11.97265625" customWidth="1"/>
-    <col min="3" max="3" width="9.953125" customWidth="1"/>
-    <col min="4" max="4" width="11.97265625" customWidth="1"/>
-    <col min="5" max="5" width="29.99609375" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2380,7 +2371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2388,70 +2379,97 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="C8" s="3">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C10" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3">
         <v>5</v>
@@ -2460,117 +2478,117 @@
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>15</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3">
         <v>6</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="D15" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D16" s="3">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="E17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3">
-        <v>5</v>
-      </c>
-      <c r="D15" s="3">
-        <v>15</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3">
-        <v>27</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="B18" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3">
         <v>6</v>
@@ -2579,108 +2597,57 @@
         <v>18</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="3">
-        <v>6</v>
-      </c>
-      <c r="D19" s="3">
-        <v>18</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C20" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="3">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3">
-        <v>18</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="3">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3">
-        <v>21</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3">
-        <v>9</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>607</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>608</v>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>601</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -2688,7 +2655,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E25" r:id="rId1" xr:uid="{3D16AD15-F8C8-7246-B225-B6ECA04CE240}"/>
+    <hyperlink ref="E22" r:id="rId1" xr:uid="{3D16AD15-F8C8-7246-B225-B6ECA04CE240}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2697,246 +2664,246 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="D13" s="8" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="D16" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="B14" s="15" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B17" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="D16" s="8" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="D19" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B17" s="15" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="B20" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -2982,246 +2949,246 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D7" s="8" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="D10" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="B8" s="15" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="B11" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="D22" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -3267,280 +3234,280 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C20" s="7" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="D25" s="8" t="s">
         <v>475</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -3591,246 +3558,246 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -3876,280 +3843,280 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="B5" s="15" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B8" s="16" t="s">
         <v>532</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="D12" s="8" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="C20" s="7" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>569</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="D25" s="8" t="s">
         <v>576</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="7" t="s">
-        <v>581</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -4200,144 +4167,144 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -4368,142 +4335,142 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C5" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4534,212 +4501,212 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D6" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4780,110 +4747,110 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4909,246 +4876,246 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -5194,212 +5161,212 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -5440,212 +5407,212 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D13" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D16" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>245</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5672,7 +5639,7 @@
     <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
     <hyperlink ref="D12" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
     <hyperlink ref="D13" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
-    <hyperlink ref="D14" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="D14" r:id="rId10" location="named-entities" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
     <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
     <hyperlink ref="D16" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
     <hyperlink ref="D17" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
@@ -5686,352 +5653,360 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D10" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D12" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="D13" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="B11" s="15" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="B14" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="D14" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
+      <c r="D15" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="C20" s="7" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="D25" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="C23" s="7" t="s">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="B26" s="16" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="7" t="s">
+      <c r="C26" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D26" s="8" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="7" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D27" s="8" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="D28" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="C26" s="7" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="B29" s="16" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D29" s="8" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="7" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D30" s="8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="D31" s="8" t="s">
         <v>313</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>319</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A26:A28"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
@@ -6043,14 +6018,6 @@
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="A26:A28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
@@ -6088,96 +6055,96 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.98046875" customWidth="1"/>
-    <col min="2" max="2" width="45.0625" customWidth="1"/>
-    <col min="3" max="3" width="34.97265625" customWidth="1"/>
-    <col min="4" max="4" width="69.94921875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>332</v>
       </c>
     </row>
   </sheetData>
